--- a/data/trans_orig/ProblemasDormirP33b-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario en 2023</t>
+          <t>Población con problemas para dormir a diario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58829</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92930</t>
+          <t>91054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107746</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155222</t>
+          <t>153978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180586</t>
+          <t>181844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235224</t>
+          <t>232003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>542511</t>
+          <t>544387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>576612</t>
+          <t>575987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570108</t>
+          <t>571352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617584</t>
+          <t>617998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1125548</t>
+          <t>1128769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1180186</t>
+          <t>1178928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53114</t>
+          <t>50283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143459</t>
+          <t>142705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180017</t>
+          <t>180099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219475</t>
+          <t>222633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199291</t>
+          <t>204001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354196</t>
+          <t>356637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1049405</t>
+          <t>1050159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1139750</t>
+          <t>1142581</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>739176</t>
+          <t>736018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>778634</t>
+          <t>778552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1797320</t>
+          <t>1794879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1952225</t>
+          <t>1947515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64464</t>
+          <t>64707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98733</t>
+          <t>101703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63088</t>
+          <t>58277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159968</t>
+          <t>157228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131776</t>
+          <t>136995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238577</t>
+          <t>241677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605947</t>
+          <t>602977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640216</t>
+          <t>639973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>773398</t>
+          <t>776138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>870278</t>
+          <t>875089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1399469</t>
+          <t>1396369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1506270</t>
+          <t>1501051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133700</t>
+          <t>132688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181527</t>
+          <t>178329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200603</t>
+          <t>195053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>275354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352369</t>
+          <t>346202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>436300</t>
+          <t>434841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>745304</t>
+          <t>748502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>793131</t>
+          <t>794143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>822083</t>
+          <t>819578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>894329</t>
+          <t>899879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1585463</t>
+          <t>1586922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1669394</t>
+          <t>1675561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333670</t>
+          <t>325701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>466160</t>
+          <t>467253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>564511</t>
+          <t>562143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>760768</t>
+          <t>762810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>966335</t>
+          <t>957431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1205571</t>
+          <t>1205638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2993657</t>
+          <t>2992564</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3126147</t>
+          <t>3134116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2951512</t>
+          <t>2949470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3147769</t>
+          <t>3150137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5966526</t>
+          <t>5966459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6205762</t>
+          <t>6214666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProblemasDormirP33b-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73850</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59454</t>
+          <t>64548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91054</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>134990</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107332</t>
+          <t>130817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153978</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>208840</t>
+          <t>229576</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181844</t>
+          <t>206567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232003</t>
+          <t>257226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>561591</t>
+          <t>609945</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>544387</t>
+          <t>588231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>575987</t>
+          <t>626162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>590340</t>
+          <t>585369</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>571352</t>
+          <t>568739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617998</t>
+          <t>603363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1151932</t>
+          <t>1195313</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1128769</t>
+          <t>1167663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1178928</t>
+          <t>1218322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>105723</t>
+          <t>118202</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>97936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142705</t>
+          <t>142534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>200836</t>
+          <t>225669</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180099</t>
+          <t>203148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>222633</t>
+          <t>247463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>306559</t>
+          <t>343871</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204001</t>
+          <t>312161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>356637</t>
+          <t>380511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1087141</t>
+          <t>930715</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1050159</t>
+          <t>906383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1142581</t>
+          <t>950981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>757815</t>
+          <t>845805</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>736018</t>
+          <t>824011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>778552</t>
+          <t>868326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1844957</t>
+          <t>1776520</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1794879</t>
+          <t>1739880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1947515</t>
+          <t>1808230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81023</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101703</t>
+          <t>110004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>117834</t>
+          <t>135789</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>118299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157228</t>
+          <t>156053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>198857</t>
+          <t>224973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136995</t>
+          <t>197950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241677</t>
+          <t>253394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>623657</t>
+          <t>713889</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602977</t>
+          <t>693069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639973</t>
+          <t>731089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>815532</t>
+          <t>676470</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>776138</t>
+          <t>656206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>875089</t>
+          <t>693960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1439189</t>
+          <t>1390359</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1396369</t>
+          <t>1361938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1501051</t>
+          <t>1417382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>169716</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132688</t>
+          <t>147343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178329</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>243634</t>
+          <t>267847</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195053</t>
+          <t>243721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275354</t>
+          <t>293680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>398752</t>
+          <t>437564</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346202</t>
+          <t>404024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>434841</t>
+          <t>474300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>771712</t>
+          <t>820346</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>795631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>794143</t>
+          <t>842719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>851298</t>
+          <t>851194</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>819578</t>
+          <t>825361</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>899879</t>
+          <t>875320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1623011</t>
+          <t>1671540</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1586922</t>
+          <t>1634804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1675561</t>
+          <t>1705080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>457867</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>325701</t>
+          <t>417781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>467253</t>
+          <t>501711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>697294</t>
+          <t>778116</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>562143</t>
+          <t>738160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>762810</t>
+          <t>822248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1113009</t>
+          <t>1235984</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>957431</t>
+          <t>1172707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1205638</t>
+          <t>1295263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3044102</t>
+          <t>3074895</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2992564</t>
+          <t>3031051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3134116</t>
+          <t>3114981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3014986</t>
+          <t>2958838</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2949470</t>
+          <t>2914706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3150137</t>
+          <t>2998794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6059088</t>
+          <t>6033732</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5966459</t>
+          <t>5974453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6214666</t>
+          <t>6097009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
